--- a/technology_surveys/027_ai_mentor_customization_survey--technology_surveys.xlsx
+++ b/technology_surveys/027_ai_mentor_customization_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -963,12 +963,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'software_development_/_coding',_'value':_'coding'}</t>
+          <t>software_development_/_coding</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Software Development / Coding', 'value': 'coding'}</t>
+          <t>Software Development / Coding</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'business_strategy_&amp;_entrepreneurship',_'value':_'business'}</t>
+          <t>business_strategy_&amp;_entrepreneurship</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Business Strategy &amp; Entrepreneurship', 'value': 'business'}</t>
+          <t>Business Strategy &amp; Entrepreneurship</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'creative_writing_&amp;_content',_'value':_'writing'}</t>
+          <t>creative_writing_&amp;_content</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Creative Writing &amp; Content', 'value': 'writing'}</t>
+          <t>Creative Writing &amp; Content</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'data_science_&amp;_analytics',_'value':_'data_science'}</t>
+          <t>data_science_&amp;_analytics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Data Science &amp; Analytics', 'value': 'data_science'}</t>
+          <t>Data Science &amp; Analytics</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'personal_growth_&amp;_wellness',_'value':_'wellness'}</t>
+          <t>personal_growth_&amp;_wellness</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Personal Growth &amp; Wellness', 'value': 'wellness'}</t>
+          <t>Personal Growth &amp; Wellness</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'academic_research',_'value':_'research'}</t>
+          <t>academic_research</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Academic Research', 'value': 'research'}</t>
+          <t>Academic Research</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'novice_(just_starting)',_'value':_'novice'}</t>
+          <t>novice_(just_starting)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Novice (Just starting)', 'value': 'novice'}</t>
+          <t>Novice (Just starting)</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'intermediate_(have_foundational_knowledge)',_'value':_'intermediate'}</t>
+          <t>intermediate_(have_foundational_knowledge)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Intermediate (Have foundational knowledge)', 'value': 'intermediate'}</t>
+          <t>Intermediate (Have foundational knowledge)</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'advanced_(proficient_/_professional)',_'value':_'advanced'}</t>
+          <t>advanced_(proficient_/_professional)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Advanced (Proficient / Professional)', 'value': 'advanced'}</t>
+          <t>Advanced (Proficient / Professional)</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'expert_(specialized_/_lead_role)',_'value':_'expert'}</t>
+          <t>expert_(specialized_/_lead_role)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Expert (Specialized / Lead role)', 'value': 'expert'}</t>
+          <t>Expert (Specialized / Lead role)</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'encouraging_&amp;_supportive_(positive_reinforcement)',_'value':_'supportive'}</t>
+          <t>encouraging_&amp;_supportive_(positive_reinforcement)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Encouraging &amp; Supportive (Positive reinforcement)', 'value': 'supportive'}</t>
+          <t>Encouraging &amp; Supportive (Positive reinforcement)</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'direct_&amp;_critical_(no-nonsense_feedback)',_'value':_'direct'}</t>
+          <t>direct_&amp;_critical_(no-nonsense_feedback)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Direct &amp; Critical (No-nonsense feedback)', 'value': 'direct'}</t>
+          <t>Direct &amp; Critical (No-nonsense feedback)</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'socratic_(guides_you_with_questions)',_'value':_'socratic'}</t>
+          <t>socratic_(guides_you_with_questions)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Socratic (Guides you with questions)', 'value': 'socratic'}</t>
+          <t>Socratic (Guides you with questions)</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'analytical_(data_and_evidence_focused)',_'value':_'analytical'}</t>
+          <t>analytical_(data_and_evidence_focused)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Analytical (Data and evidence focused)', 'value': 'analytical'}</t>
+          <t>Analytical (Data and evidence focused)</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'professional_/_formal',_'value':_'professional'}</t>
+          <t>professional_/_formal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Professional / Formal', 'value': 'professional'}</t>
+          <t>Professional / Formal</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'casual_/_friendly',_'value':_'casual'}</t>
+          <t>casual_/_friendly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Casual / Friendly', 'value': 'casual'}</t>
+          <t>Casual / Friendly</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'academic_/_serious',_'value':_'academic'}</t>
+          <t>academic_/_serious</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Academic / Serious', 'value': 'academic'}</t>
+          <t>Academic / Serious</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'quirky_/_humorous',_'value':_'quirky'}</t>
+          <t>quirky_/_humorous</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Quirky / Humorous', 'value': 'quirky'}</t>
+          <t>Quirky / Humorous</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'daily_(morning/evening_sync)',_'value':_'daily'}</t>
+          <t>daily_(morning/evening_sync)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Daily (Morning/Evening Sync)', 'value': 'daily'}</t>
+          <t>Daily (Morning/Evening Sync)</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'twice_weekly',_'value':_'biweekly'}</t>
+          <t>twice_weekly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Twice Weekly', 'value': 'biweekly'}</t>
+          <t>Twice Weekly</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'weekly_summary',_'value':_'weekly'}</t>
+          <t>weekly_summary</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly Summary', 'value': 'weekly'}</t>
+          <t>Weekly Summary</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'never_(i_will_initiate_all_contact)',_'value':_'on_demand'}</t>
+          <t>never_(i_will_initiate_all_contact)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Never (I will initiate all contact)', 'value': 'on_demand'}</t>
+          <t>Never (I will initiate all contact)</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'high-level_/_conceptual',_'value':_'high_level'}</t>
+          <t>high-level_/_conceptual</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'High-level / Conceptual', 'value': 'high_level'}</t>
+          <t>High-level / Conceptual</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'standard_/_balanced',_'value':_'standard'}</t>
+          <t>standard_/_balanced</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Standard / Balanced', 'value': 'standard'}</t>
+          <t>Standard / Balanced</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'deep-dive_/_technical_details',_'value':_'deep_dive'}</t>
+          <t>deep-dive_/_technical_details</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Deep-dive / Technical details', 'value': 'deep_dive'}</t>
+          <t>Deep-dive / Technical details</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'text_chat',_'value':_'text'}</t>
+          <t>text_chat</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Text Chat', 'value': 'text'}</t>
+          <t>Text Chat</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'voice_/_audio_messages',_'value':_'voice'}</t>
+          <t>voice_/_audio_messages</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Voice / Audio Messages', 'value': 'voice'}</t>
+          <t>Voice / Audio Messages</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'code_review_/_code_snippets',_'value':_'code'}</t>
+          <t>code_review_/_code_snippets</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Code Review / Code Snippets', 'value': 'code'}</t>
+          <t>Code Review / Code Snippets</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'visual_/_diagrams',_'value':_'visual'}</t>
+          <t>visual_/_diagrams</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Visual / Diagrams', 'value': 'visual'}</t>
+          <t>Visual / Diagrams</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'google_calendar',_'value':_'calendar'}</t>
+          <t>google_calendar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Google Calendar', 'value': 'calendar'}</t>
+          <t>Google Calendar</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'github_/_gitlab',_'value':_'github'}</t>
+          <t>github_/_gitlab</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'GitHub / GitLab', 'value': 'github'}</t>
+          <t>GitHub / GitLab</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'notion_/_obsidian',_'value':_'docs'}</t>
+          <t>notion_/_obsidian</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Notion / Obsidian', 'value': 'docs'}</t>
+          <t>Notion / Obsidian</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'slack_/_discord',_'value':_'chat_apps'}</t>
+          <t>slack_/_discord</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Slack / Discord', 'value': 'chat_apps'}</t>
+          <t>Slack / Discord</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'full_memory_(retain_all_context_indefinitely)',_'value':_'full_memory'}</t>
+          <t>full_memory_(retain_all_context_indefinitely)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Full Memory (Retain all context indefinitely)', 'value': 'full_memory'}</t>
+          <t>Full Memory (Retain all context indefinitely)</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'session-only_memory_(forget_after_each_topic)',_'value':_'session_only'}</t>
+          <t>session-only_memory_(forget_after_each_topic)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Session-only Memory (Forget after each topic)', 'value': 'session_only'}</t>
+          <t>Session-only Memory (Forget after each topic)</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'personalized_(keep_goals,_forget_small_talk)',_'value':_'personalized'}</t>
+          <t>personalized_(keep_goals,_forget_small_talk)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Personalized (Keep goals, forget small talk)', 'value': 'personalized'}</t>
+          <t>Personalized (Keep goals, forget small talk)</t>
         </is>
       </c>
     </row>
